--- a/Slides/data/Aula-Pratica-AAS-Planilha-Analise-Semiautomatica-Exemplo-Sanquetta-et-al-2023-Dados-Campo-Simulados.xlsx
+++ b/Slides/data/Aula-Pratica-AAS-Planilha-Analise-Semiautomatica-Exemplo-Sanquetta-et-al-2023-Dados-Campo-Simulados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/37cd5d8700b5386d/GitHub/FL03039-Inventario-Florestal/Slides/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="201" documentId="13_ncr:1_{FBDD67E5-22CB-4132-A16F-019A20304AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5E08682-332D-49A4-AFE6-9EA1799E5F7C}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="13_ncr:1_{FBDD67E5-22CB-4132-A16F-019A20304AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9767B08-856B-487E-A349-C5D18A596B59}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId4"/>
+    <pivotCache cacheId="4" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1023,6 +1023,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1045,9 +1048,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -14613,7 +14613,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9207DE16-24D4-467B-A18C-5BECEC5E7972}" name="Tabela dinâmica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9207DE16-24D4-467B-A18C-5BECEC5E7972}" name="Tabela dinâmica2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B2:C19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" showAll="0">
@@ -50520,10 +50520,10 @@
       <c r="B3" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="61" t="s">
+      <c r="C3" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="62"/>
+      <c r="D3" s="63"/>
       <c r="F3" s="7"/>
       <c r="G3" s="5" t="s">
         <v>42</v>
@@ -50543,23 +50543,23 @@
       <c r="K5" s="8"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="67"/>
-      <c r="D6" s="68"/>
-      <c r="F6" s="66" t="s">
+      <c r="C6" s="68"/>
+      <c r="D6" s="69"/>
+      <c r="F6" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="67"/>
-      <c r="H6" s="68"/>
-      <c r="J6" s="66" t="s">
+      <c r="G6" s="68"/>
+      <c r="H6" s="69"/>
+      <c r="J6" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="69"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="46"/>
@@ -50618,7 +50618,7 @@
         <v>20.85018366491429</v>
       </c>
       <c r="D9" s="52">
-        <f t="shared" ref="D9:D24" si="0">C9*G$12</f>
+        <f>C9*G$12</f>
         <v>347.50306108190489</v>
       </c>
       <c r="E9" s="40"/>
@@ -50658,7 +50658,7 @@
         <v>19.469997627368215</v>
       </c>
       <c r="D10" s="52">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D9:D24" si="0">C10*G$12</f>
         <v>324.49996045613693</v>
       </c>
       <c r="E10" s="40"/>
@@ -50705,7 +50705,7 @@
       <c r="F11" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="69">
+      <c r="G11" s="61">
         <f>COUNT(C9:C48)</f>
         <v>16</v>
       </c>
@@ -50971,11 +50971,11 @@
         <v>480.66361342224695</v>
       </c>
       <c r="E18" s="40"/>
-      <c r="F18" s="66" t="s">
+      <c r="F18" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="G18" s="67"/>
-      <c r="H18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="69"/>
       <c r="J18" s="16" t="s">
         <v>25</v>
       </c>
@@ -51050,11 +51050,11 @@
         <v>413.01255703252696</v>
       </c>
       <c r="E20" s="40"/>
-      <c r="F20" s="63" t="s">
+      <c r="F20" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="64"/>
-      <c r="H20" s="65"/>
+      <c r="G20" s="65"/>
+      <c r="H20" s="66"/>
       <c r="J20" s="16" t="s">
         <v>17</v>
       </c>
@@ -51314,11 +51314,11 @@
       </c>
       <c r="C27" s="38"/>
       <c r="D27" s="42"/>
-      <c r="F27" s="63" t="s">
+      <c r="F27" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="G27" s="64"/>
-      <c r="H27" s="65"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="66"/>
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
       <c r="M27" s="11"/>
@@ -51520,7 +51520,7 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="K23 K26" evalError="1"/>
-    <ignoredError sqref="D9:D24" formula="1"/>
+    <ignoredError sqref="D10:D24" formula="1"/>
   </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
